--- a/efficiency_speedup/results.xlsx
+++ b/efficiency_speedup/results.xlsx
@@ -9,17 +9,17 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12312"/>
   </bookViews>
   <sheets>
     <sheet name="results" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="9">
   <si>
     <t>Processes</t>
   </si>
@@ -33,13 +33,19 @@
     <t>Total Area</t>
   </si>
   <si>
+    <t>1- COS(b)</t>
+  </si>
+  <si>
     <t>Elapsed Time (us)</t>
   </si>
   <si>
-    <t>1- COS(b)</t>
+    <t>Error</t>
   </si>
   <si>
-    <t>ERROR</t>
+    <t>S</t>
+  </si>
+  <si>
+    <t>E</t>
   </si>
 </sst>
 </file>
@@ -523,8 +529,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -608,11 +615,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>results!$H$11</c:f>
+              <c:f>results!$E$15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Elapsed Time (us)</c:v>
+                  <c:v>Error</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -643,7 +650,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>results!$G$12:$G$19</c:f>
+              <c:f>results!$D$16:$D$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -676,33 +683,33 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>results!$H$12:$H$19</c:f>
+              <c:f>results!$E$16:$E$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>159000000</c:v>
+                  <c:v>1.4257000000017506E-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>87000000</c:v>
+                  <c:v>4.2570000000630159E-6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>67000000</c:v>
+                  <c:v>3.7429999999449848E-6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>62000000</c:v>
+                  <c:v>1.725699999999275E-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>49000000</c:v>
+                  <c:v>7.4299999996974009E-7</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>51000000</c:v>
+                  <c:v>1.2569999999767489E-6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>50000000</c:v>
+                  <c:v>2.2570000000055046E-6</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>59000000</c:v>
+                  <c:v>4.2570000000630159E-6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -710,7 +717,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6B50-4A51-90CC-6C41E56F3150}"/>
+              <c16:uniqueId val="{00000000-B9CF-44C5-B0EF-BEB03B39C000}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -722,11 +729,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1642797840"/>
-        <c:axId val="1642795760"/>
+        <c:axId val="1859972463"/>
+        <c:axId val="1859972879"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1642797840"/>
+        <c:axId val="1859972463"/>
         <c:scaling>
           <c:logBase val="2"/>
           <c:orientation val="minMax"/>
@@ -854,17 +861,17 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1642795760"/>
+        <c:crossAx val="1859972879"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1642795760"/>
+        <c:axId val="1859972879"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="l"/>
+        <c:axPos val="r"/>
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -914,7 +921,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Elapsed Time (us)</a:t>
+                  <a:t>Error</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -986,42 +993,9 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1642797840"/>
-        <c:crosses val="autoZero"/>
+        <c:crossAx val="1859972463"/>
+        <c:crosses val="max"/>
         <c:crossBetween val="midCat"/>
-        <c:dispUnits>
-          <c:builtInUnit val="millions"/>
-          <c:dispUnitsLbl>
-            <c:layout/>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-          </c:dispUnitsLbl>
-        </c:dispUnits>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1125,11 +1099,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>results!$H$24</c:f>
+              <c:f>results!$E$30</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>ERROR</c:v>
+                  <c:v>Elapsed Time (us)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1160,7 +1134,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>results!$G$25:$G$32</c:f>
+              <c:f>results!$D$31:$D$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -1193,33 +1167,33 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>results!$H$25:$H$32</c:f>
+              <c:f>results!$E$31:$E$38</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>6.0000000000000002E-6</c:v>
+                  <c:v>160000000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.2E-5</c:v>
+                  <c:v>86000000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.6027999999999999E-2</c:v>
+                  <c:v>104000000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.8403999999999998E-2</c:v>
+                  <c:v>64000000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.14288000000000001</c:v>
+                  <c:v>48000000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.30119600000000002</c:v>
+                  <c:v>54000000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.26306800000000002</c:v>
+                  <c:v>54000000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.6565300000000001</c:v>
+                  <c:v>64000000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1227,7 +1201,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D865-4EE3-AF22-7C6D98109CDF}"/>
+              <c16:uniqueId val="{00000000-30E1-4B53-A541-6400B1EDC391}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1239,11 +1213,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1546170864"/>
-        <c:axId val="1546174192"/>
+        <c:axId val="2131349263"/>
+        <c:axId val="2131358831"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1546170864"/>
+        <c:axId val="2131349263"/>
         <c:scaling>
           <c:logBase val="2"/>
           <c:orientation val="minMax"/>
@@ -1371,12 +1345,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1546174192"/>
+        <c:crossAx val="2131358831"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1546174192"/>
+        <c:axId val="2131358831"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1431,7 +1405,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>ERROR</a:t>
+                  <a:t>Elapsed Time (us)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -1503,7 +1477,996 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1546170864"/>
+        <c:crossAx val="2131349263"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:dispUnits>
+          <c:builtInUnit val="millions"/>
+          <c:dispUnitsLbl>
+            <c:layout/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+          </c:dispUnitsLbl>
+        </c:dispUnits>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>results!$Q$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>S</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>results!$P$14:$P$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>results!$Q$14:$Q$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="1">
+                  <c:v>1.8604651162790697</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5384615384615385</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.3333333333333335</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.9629629629629628</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.9629629629629628</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4276-453C-A84F-FB07D2791F5C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1098282255"/>
+        <c:axId val="1098284335"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1098282255"/>
+        <c:scaling>
+          <c:logBase val="2"/>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Processes</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1098284335"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1098284335"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Speeedup</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1098282255"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>results!$Q$40</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>E</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>results!$P$41:$P$48</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>results!$Q$41:$Q$48</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="1">
+                  <c:v>0.93023255813953487</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.38461538461538464</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3125</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.20833333333333334</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.2592592592592587E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.6296296296296294E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.953125E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CC2B-4AD9-8334-8AF261566F62}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1350429023"/>
+        <c:axId val="1350439007"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1350429023"/>
+        <c:scaling>
+          <c:logBase val="2"/>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Processes</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1350439007"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1350439007"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Efficiency</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1350429023"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1664,6 +2627,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -2696,20 +3739,1052 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>487680</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>80010</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>83820</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>163830</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>182880</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>80010</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>243840</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>163830</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2730,16 +4805,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>335280</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>403860</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>163830</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>563880</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>163830</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2753,6 +4828,66 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>480060</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>518160</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>118110</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>118110</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3024,13 +5159,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:Q48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3044,16 +5179,22 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
       </c>
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3064,19 +5205,20 @@
         <v>10000000</v>
       </c>
       <c r="D2">
-        <v>0.62201600000000001</v>
+        <v>0.62200800000000001</v>
       </c>
       <c r="E2">
-        <v>159000000</v>
+        <v>160000000</v>
       </c>
       <c r="F2">
         <v>0.62202225700000002</v>
       </c>
       <c r="G2">
-        <v>6.0000000000000002E-6</v>
+        <f t="shared" ref="G2:G9" si="0">ABS(D2-F2)</f>
+        <v>1.4257000000017506E-5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3087,19 +5229,28 @@
         <v>10000000</v>
       </c>
       <c r="D3">
-        <v>0.62200999999999995</v>
+        <v>0.62201799999999996</v>
       </c>
       <c r="E3">
-        <v>87000000</v>
+        <v>86000000</v>
       </c>
       <c r="F3">
         <v>0.62202225700000002</v>
       </c>
       <c r="G3">
-        <v>1.2E-5</v>
+        <f t="shared" si="0"/>
+        <v>4.2570000000630159E-6</v>
+      </c>
+      <c r="H3" s="1">
+        <f>E2/E3</f>
+        <v>1.8604651162790697</v>
+      </c>
+      <c r="I3">
+        <f>H3/2</f>
+        <v>0.93023255813953487</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>4</v>
       </c>
@@ -3110,19 +5261,28 @@
         <v>10000000</v>
       </c>
       <c r="D4">
-        <v>0.66805000000000003</v>
+        <v>0.62202599999999997</v>
       </c>
       <c r="E4">
-        <v>67000000</v>
+        <v>104000000</v>
       </c>
       <c r="F4">
         <v>0.62202225700000002</v>
       </c>
       <c r="G4">
-        <v>4.6027999999999999E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.7429999999449848E-6</v>
+      </c>
+      <c r="H4">
+        <f>E2/E4</f>
+        <v>1.5384615384615385</v>
+      </c>
+      <c r="I4">
+        <f>H4/4</f>
+        <v>0.38461538461538464</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>8</v>
       </c>
@@ -3133,19 +5293,28 @@
         <v>10000000</v>
       </c>
       <c r="D5">
-        <v>0.68042599999999998</v>
+        <v>0.62200500000000003</v>
       </c>
       <c r="E5">
-        <v>62000000</v>
+        <v>64000000</v>
       </c>
       <c r="F5">
         <v>0.62202225700000002</v>
       </c>
       <c r="G5">
-        <v>5.8403999999999998E-2</v>
+        <f t="shared" si="0"/>
+        <v>1.725699999999275E-5</v>
+      </c>
+      <c r="H5">
+        <f>E2/E5</f>
+        <v>2.5</v>
+      </c>
+      <c r="I5">
+        <f>H5/8</f>
+        <v>0.3125</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>16</v>
       </c>
@@ -3156,19 +5325,28 @@
         <v>10000000</v>
       </c>
       <c r="D6">
-        <v>0.76490199999999997</v>
+        <v>0.62202299999999999</v>
       </c>
       <c r="E6">
-        <v>49000000</v>
+        <v>48000000</v>
       </c>
       <c r="F6">
         <v>0.62202225700000002</v>
       </c>
       <c r="G6">
-        <v>0.14288000000000001</v>
+        <f t="shared" si="0"/>
+        <v>7.4299999996974009E-7</v>
+      </c>
+      <c r="H6">
+        <f>E2/E6</f>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="I6">
+        <f>H6/16</f>
+        <v>0.20833333333333334</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>32</v>
       </c>
@@ -3179,19 +5357,28 @@
         <v>10000000</v>
       </c>
       <c r="D7">
-        <v>0.92321799999999998</v>
+        <v>0.62202100000000005</v>
       </c>
       <c r="E7">
-        <v>51000000</v>
+        <v>54000000</v>
       </c>
       <c r="F7">
         <v>0.62202225700000002</v>
       </c>
       <c r="G7">
-        <v>0.30119600000000002</v>
+        <f t="shared" si="0"/>
+        <v>1.2569999999767489E-6</v>
+      </c>
+      <c r="H7">
+        <f>E2/E7</f>
+        <v>2.9629629629629628</v>
+      </c>
+      <c r="I7">
+        <f>H7/32</f>
+        <v>9.2592592592592587E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>64</v>
       </c>
@@ -3202,19 +5389,28 @@
         <v>10000000</v>
       </c>
       <c r="D8">
-        <v>0.88509000000000004</v>
+        <v>0.62202000000000002</v>
       </c>
       <c r="E8">
-        <v>50000000</v>
+        <v>54000000</v>
       </c>
       <c r="F8">
         <v>0.62202225700000002</v>
       </c>
       <c r="G8">
-        <v>0.26306800000000002</v>
+        <f t="shared" si="0"/>
+        <v>2.2570000000055046E-6</v>
+      </c>
+      <c r="H8">
+        <f>E2/E8</f>
+        <v>2.9629629629629628</v>
+      </c>
+      <c r="I8">
+        <f>H8/64</f>
+        <v>4.6296296296296294E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>128</v>
       </c>
@@ -3225,160 +5421,283 @@
         <v>10000000</v>
       </c>
       <c r="D9">
-        <v>1.9876750000000001</v>
+        <v>0.62201799999999996</v>
       </c>
       <c r="E9">
-        <v>59000000</v>
+        <v>64000000</v>
       </c>
       <c r="F9">
         <v>0.62202225700000002</v>
       </c>
       <c r="G9">
-        <v>1.6565300000000001</v>
+        <f t="shared" si="0"/>
+        <v>4.2570000000630159E-6</v>
+      </c>
+      <c r="H9">
+        <f>E2/E9</f>
+        <v>2.5</v>
+      </c>
+      <c r="I9">
+        <f>H9/128</f>
+        <v>1.953125E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G11" t="s">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="P13" t="s">
         <v>0</v>
       </c>
-      <c r="H11" t="s">
+      <c r="Q13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D15" t="s">
+        <v>0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+      <c r="P15">
+        <v>2</v>
+      </c>
+      <c r="Q15">
+        <v>1.8604651162790697</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1.4257000000017506E-5</v>
+      </c>
+      <c r="P16">
         <v>4</v>
       </c>
+      <c r="Q16">
+        <v>1.5384615384615385</v>
+      </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G12">
+    <row r="17" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <v>4.2570000000630159E-6</v>
+      </c>
+      <c r="P17">
+        <v>8</v>
+      </c>
+      <c r="Q17">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="18" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D18">
+        <v>4</v>
+      </c>
+      <c r="E18">
+        <v>3.7429999999449848E-6</v>
+      </c>
+      <c r="P18">
+        <v>16</v>
+      </c>
+      <c r="Q18">
+        <v>3.3333333333333335</v>
+      </c>
+    </row>
+    <row r="19" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D19">
+        <v>8</v>
+      </c>
+      <c r="E19">
+        <v>1.725699999999275E-5</v>
+      </c>
+      <c r="P19">
+        <v>32</v>
+      </c>
+      <c r="Q19">
+        <v>2.9629629629629628</v>
+      </c>
+    </row>
+    <row r="20" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D20">
+        <v>16</v>
+      </c>
+      <c r="E20">
+        <v>7.4299999996974009E-7</v>
+      </c>
+      <c r="P20">
+        <v>64</v>
+      </c>
+      <c r="Q20">
+        <v>2.9629629629629628</v>
+      </c>
+    </row>
+    <row r="21" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D21">
+        <v>32</v>
+      </c>
+      <c r="E21">
+        <v>1.2569999999767489E-6</v>
+      </c>
+      <c r="P21">
+        <v>128</v>
+      </c>
+      <c r="Q21">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="22" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D22">
+        <v>64</v>
+      </c>
+      <c r="E22">
+        <v>2.2570000000055046E-6</v>
+      </c>
+    </row>
+    <row r="23" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D23">
+        <v>128</v>
+      </c>
+      <c r="E23">
+        <v>4.2570000000630159E-6</v>
+      </c>
+    </row>
+    <row r="30" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D30" t="s">
+        <v>0</v>
+      </c>
+      <c r="E30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D31">
         <v>1</v>
       </c>
-      <c r="H12">
-        <v>159000000</v>
+      <c r="E31">
+        <v>160000000</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G13">
+    <row r="32" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D32">
         <v>2</v>
       </c>
-      <c r="H13">
-        <v>87000000</v>
+      <c r="E32">
+        <v>86000000</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G14">
+    <row r="33" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D33">
         <v>4</v>
       </c>
-      <c r="H14">
-        <v>67000000</v>
+      <c r="E33">
+        <v>104000000</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G15">
+    <row r="34" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D34">
         <v>8</v>
       </c>
-      <c r="H15">
-        <v>62000000</v>
+      <c r="E34">
+        <v>64000000</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G16">
+    <row r="35" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D35">
         <v>16</v>
       </c>
-      <c r="H16">
-        <v>49000000</v>
+      <c r="E35">
+        <v>48000000</v>
       </c>
     </row>
-    <row r="17" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G17">
+    <row r="36" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D36">
         <v>32</v>
       </c>
-      <c r="H17">
-        <v>51000000</v>
+      <c r="E36">
+        <v>54000000</v>
       </c>
     </row>
-    <row r="18" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G18">
+    <row r="37" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D37">
         <v>64</v>
       </c>
-      <c r="H18">
-        <v>50000000</v>
+      <c r="E37">
+        <v>54000000</v>
       </c>
     </row>
-    <row r="19" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G19">
+    <row r="38" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D38">
         <v>128</v>
       </c>
-      <c r="H19">
-        <v>59000000</v>
+      <c r="E38">
+        <v>64000000</v>
       </c>
     </row>
-    <row r="24" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G24" t="s">
+    <row r="40" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="P40" t="s">
         <v>0</v>
       </c>
-      <c r="H24" t="s">
-        <v>6</v>
+      <c r="Q40" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="25" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G25">
-        <v>1</v>
-      </c>
-      <c r="H25">
-        <v>6.0000000000000002E-6</v>
+    <row r="42" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="P42">
+        <v>2</v>
+      </c>
+      <c r="Q42">
+        <v>0.93023255813953487</v>
       </c>
     </row>
-    <row r="26" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G26">
-        <v>2</v>
-      </c>
-      <c r="H26">
-        <v>1.2E-5</v>
+    <row r="43" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="P43">
+        <v>4</v>
+      </c>
+      <c r="Q43">
+        <v>0.38461538461538464</v>
       </c>
     </row>
-    <row r="27" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G27">
-        <v>4</v>
-      </c>
-      <c r="H27">
-        <v>4.6027999999999999E-2</v>
+    <row r="44" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="P44">
+        <v>8</v>
+      </c>
+      <c r="Q44">
+        <v>0.3125</v>
       </c>
     </row>
-    <row r="28" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G28">
-        <v>8</v>
-      </c>
-      <c r="H28">
-        <v>5.8403999999999998E-2</v>
+    <row r="45" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="P45">
+        <v>16</v>
+      </c>
+      <c r="Q45">
+        <v>0.20833333333333334</v>
       </c>
     </row>
-    <row r="29" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G29">
-        <v>16</v>
-      </c>
-      <c r="H29">
-        <v>0.14288000000000001</v>
+    <row r="46" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="P46">
+        <v>32</v>
+      </c>
+      <c r="Q46">
+        <v>9.2592592592592587E-2</v>
       </c>
     </row>
-    <row r="30" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G30">
-        <v>32</v>
-      </c>
-      <c r="H30">
-        <v>0.30119600000000002</v>
+    <row r="47" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="P47">
+        <v>64</v>
+      </c>
+      <c r="Q47">
+        <v>4.6296296296296294E-2</v>
       </c>
     </row>
-    <row r="31" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G31">
-        <v>64</v>
-      </c>
-      <c r="H31">
-        <v>0.26306800000000002</v>
-      </c>
-    </row>
-    <row r="32" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G32">
+    <row r="48" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="P48">
         <v>128</v>
       </c>
-      <c r="H32">
-        <v>1.6565300000000001</v>
+      <c r="Q48">
+        <v>1.953125E-2</v>
       </c>
     </row>
   </sheetData>

--- a/efficiency_speedup/results.xlsx
+++ b/efficiency_speedup/results.xlsx
@@ -4865,16 +4865,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>518160</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>118110</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>502920</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>213360</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>118110</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>53340</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
